--- a/UK_CoP_TitleLists/Cogitatio_Gold_scifreeimport.xlsx
+++ b/UK_CoP_TitleLists/Cogitatio_Gold_scifreeimport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livenorthumbriaac.sharepoint.com/sites/LibraryScholarlyCommunications/Shared Documents/General/SciFree/COP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livenorthumbriaac.sharepoint.com/sites/LibraryScholarlyCommunications/Shared Documents/General/SciFree/COP/202605_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{FA63B131-D01A-4294-9B1F-0F98243C8D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C293D8B7-7514-4855-9AE3-B328C6FCEBCF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{FA63B131-D01A-4294-9B1F-0F98243C8D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16A55F4-EEF8-4301-9408-351257F65D1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal List" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>Journal Title</t>
   </si>
@@ -218,6 +218,21 @@
   </si>
   <si>
     <t>https://www.cogitatiopress.com/oceanandsociety</t>
+  </si>
+  <si>
+    <t>information, mass media, journalism, press, sociology, culture, language and literature: philology. linguistics: communication. mass media, communication, communication</t>
+  </si>
+  <si>
+    <t>political science, politics, governance, state, international relations, political science: political science (general), political science, sociology and political science, public administration</t>
+  </si>
+  <si>
+    <t>social inclusion, social exclusion, education, minorities, disability, inequality, social sciences: sociology (general), social sciences, interdisciplinary, social psychology, sociology and political science</t>
+  </si>
+  <si>
+    <t>urban planning, urbanism, urban phenomena, cities, sustainability, urban, social sciences: communities. classes. races: urban groups. the city. urban sociology: city planning, urban studies, urban studies</t>
+  </si>
+  <si>
+    <t>ocean, social sciences, marine science, coastal management, blue economy, ocean governance, geography. anthropology. recreation: geography (general) | naval science | science: natural history (general): general. including nature conservation, geographical distribution, marine environments, coastal environments, maritime social sciences</t>
   </si>
 </sst>
 </file>
@@ -2001,7 +2016,9 @@
       <c r="G2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="15" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
@@ -2023,7 +2040,9 @@
       <c r="G3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="15"/>
+      <c r="H3" s="15" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -2045,7 +2064,9 @@
       <c r="G4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -2067,7 +2088,9 @@
       <c r="G5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="15" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -2089,7 +2112,9 @@
       <c r="G6" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="15" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
@@ -2699,8 +2724,28 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE339D09936DB4EBD68BB5ACEDF8699" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6dccab1b5e4922c38813fe93b1fea2f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="63019a3c-daef-4188-8d1b-c179193e327c" xmlns:ns3="92f39531-4015-4bb8-9ef9-c2f0c46bedba" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc4f685b110b27396012ae5233c6080" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="92f39531-4015-4bb8-9ef9-c2f0c46bedba" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="63019a3c-daef-4188-8d1b-c179193e327c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE339D09936DB4EBD68BB5ACEDF8699" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f64cba7528d0d5758442992a76e8ac5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="63019a3c-daef-4188-8d1b-c179193e327c" xmlns:ns3="92f39531-4015-4bb8-9ef9-c2f0c46bedba" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="593021ed1317c897b0691bd013adea50" ns2:_="" ns3:_="">
     <xsd:import namespace="63019a3c-daef-4188-8d1b-c179193e327c"/>
     <xsd:import namespace="92f39531-4015-4bb8-9ef9-c2f0c46bedba"/>
     <xsd:element name="properties">
@@ -2953,26 +2998,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="92f39531-4015-4bb8-9ef9-c2f0c46bedba" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="63019a3c-daef-4188-8d1b-c179193e327c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB2FFCD-F4AA-4949-9A95-091BF54A192C}">
   <ds:schemaRefs>
@@ -2982,7 +3007,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C848A762-E3D1-488F-BE04-D434285D5ACA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B214E58-B745-457E-9C5B-6D2B4970FFAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="92f39531-4015-4bb8-9ef9-c2f0c46bedba"/>
+    <ds:schemaRef ds:uri="63019a3c-daef-4188-8d1b-c179193e327c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA7E4F94-7875-4D3E-B301-F7464DB6636A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8924EA5F-DE22-4222-887C-3EDF37D3141E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -2998,23 +3042,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA7E4F94-7875-4D3E-B301-F7464DB6636A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B214E58-B745-457E-9C5B-6D2B4970FFAD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="92f39531-4015-4bb8-9ef9-c2f0c46bedba"/>
-    <ds:schemaRef ds:uri="63019a3c-daef-4188-8d1b-c179193e327c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>